--- a/SysSettings.xlsx
+++ b/SysSettings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Veda\Veda_models\Demo_models_Training\DemoS_001\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gaura\Documents\GitHub\DemoS_001\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F7E61BF-8230-42E1-9D2C-B16AD4DD784A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DA3BB94-89E2-4D76-9132-41913A6AB15A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" tabRatio="853" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="853" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Region-Time Slices" sheetId="16" r:id="rId1"/>
@@ -360,34 +360,26 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2237,7 +2229,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="IEA Data"/>
@@ -2372,9 +2364,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2412,9 +2404,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2447,26 +2439,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2499,26 +2474,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2692,17 +2650,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A3:J38"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="B3:J5"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.140625" customWidth="1"/>
-    <col min="2" max="2" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.1796875" customWidth="1"/>
+    <col min="2" max="2" width="19.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" s="5"/>
+    <row r="3" spans="2:10" ht="13" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
@@ -2712,8 +2669,7 @@
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="5"/>
+    <row r="4" spans="2:10" ht="13" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
@@ -2730,153 +2686,16 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" s="5"/>
-      <c r="B5" s="11" t="s">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B5" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="11" t="s">
+      <c r="H5" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="H7" s="5"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="H8" s="5"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="5"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="5"/>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" s="5"/>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" s="5"/>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" s="5"/>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" s="5"/>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" s="5"/>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" s="5"/>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" s="5"/>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" s="5"/>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" s="5"/>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29" s="5"/>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30" s="5"/>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" s="5"/>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32" s="5"/>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A33" s="5"/>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A34" s="5"/>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A35" s="5"/>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A36" s="5"/>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A37" s="5"/>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A38" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -2890,62 +2709,59 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B3:E14"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="B3:E9"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="2.42578125" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="2.42578125" customWidth="1"/>
-    <col min="6" max="6" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="2.453125" customWidth="1"/>
+    <col min="4" max="4" width="12.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="2.453125" customWidth="1"/>
+    <col min="6" max="6" width="13.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B3" s="10" t="s">
+    <row r="3" spans="2:5" ht="13" x14ac:dyDescent="0.3">
+      <c r="B3" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="9" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B4" s="23">
-        <v>2005</v>
-      </c>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23" t="s">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B4" s="17">
+        <v>20025</v>
+      </c>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="23"/>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B6" s="10" t="s">
+      <c r="E4" s="17"/>
+    </row>
+    <row r="6" spans="2:5" ht="13" x14ac:dyDescent="0.3">
+      <c r="B6" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B7" s="23">
-        <v>2005</v>
-      </c>
-      <c r="D7" s="21" t="s">
+    <row r="7" spans="2:5" ht="13" x14ac:dyDescent="0.3">
+      <c r="B7" s="17">
+        <v>2025</v>
+      </c>
+      <c r="D7" s="16" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="D8" s="22">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="D8" s="17">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="D9" s="22">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="D9" s="17">
         <v>2</v>
       </c>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B14" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -2958,37 +2774,37 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="B13:I20"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="B13:E20"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" customWidth="1"/>
-    <col min="2" max="2" width="10.140625" customWidth="1"/>
-    <col min="4" max="4" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="9.28515625" customWidth="1"/>
+    <col min="1" max="1" width="2.81640625" customWidth="1"/>
+    <col min="2" max="2" width="10.1796875" customWidth="1"/>
+    <col min="4" max="4" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="10.7265625" customWidth="1"/>
+    <col min="13" max="13" width="9.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="2:4" ht="15" x14ac:dyDescent="0.2">
-      <c r="B13" s="6" t="s">
+    <row r="13" spans="2:4" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B13" s="5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="2:4" ht="18" x14ac:dyDescent="0.25">
-      <c r="B15" s="7" t="s">
+    <row r="15" spans="2:4" ht="17.5" x14ac:dyDescent="0.35">
+      <c r="B15" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-    </row>
-    <row r="16" spans="2:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="17" spans="2:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+    </row>
+    <row r="16" spans="2:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="2:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="18" spans="2:9" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
         <v>16</v>
       </c>
@@ -3001,15 +2817,12 @@
       <c r="E18" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F18" s="5"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>2</v>
       </c>
-      <c r="C19" s="5">
+      <c r="C19">
         <v>2222</v>
       </c>
       <c r="D19" t="s">
@@ -3018,15 +2831,12 @@
       <c r="E19" t="s">
         <v>0</v>
       </c>
-      <c r="F19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
-    </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.2">
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>2</v>
       </c>
-      <c r="C20" s="5">
+      <c r="C20">
         <v>8888</v>
       </c>
       <c r="D20" t="s">
@@ -3048,27 +2858,27 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B3:E34"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="9"/>
-    <col min="2" max="2" width="12.140625" style="9" customWidth="1"/>
-    <col min="3" max="3" width="10.85546875" style="9" customWidth="1"/>
-    <col min="4" max="4" width="14" style="9" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" style="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="9"/>
+    <col min="1" max="1" width="9.1796875" style="8"/>
+    <col min="2" max="2" width="12.1796875" style="8" customWidth="1"/>
+    <col min="3" max="3" width="10.81640625" style="8" customWidth="1"/>
+    <col min="4" max="4" width="14" style="8" customWidth="1"/>
+    <col min="5" max="5" width="10.453125" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.1796875" style="8"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:5" ht="15" x14ac:dyDescent="0.2">
-      <c r="B3" s="6" t="s">
+    <row r="3" spans="2:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="B3" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B5" s="8" t="s">
+    <row r="5" spans="2:5" ht="13" x14ac:dyDescent="0.3">
+      <c r="B5" s="7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:5" ht="13" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>14</v>
       </c>
@@ -3082,182 +2892,145 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="D7" s="9" t="s">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="D7" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="E7" s="12">
-        <v>2005</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="D8" s="9" t="s">
+      <c r="E7" s="8">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="D8" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="8">
         <v>0.05</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B9" s="9" t="s">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="11">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="16"/>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="16"/>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E11" s="11"/>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E12" s="11"/>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13"/>
       <c r="C13"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14"/>
       <c r="C14"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15"/>
       <c r="C15"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-    </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B16"/>
       <c r="C16"/>
       <c r="D16"/>
-      <c r="E16" s="12"/>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17"/>
       <c r="C17"/>
       <c r="D17"/>
-      <c r="E17" s="12"/>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B18"/>
       <c r="C18"/>
       <c r="D18"/>
-      <c r="E18" s="12"/>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B19"/>
       <c r="C19"/>
       <c r="D19"/>
-      <c r="E19" s="12"/>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20"/>
-      <c r="E20" s="12"/>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B21"/>
       <c r="C21"/>
       <c r="D21"/>
-      <c r="E21" s="12"/>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B22"/>
       <c r="C22"/>
       <c r="D22"/>
-      <c r="E22" s="12"/>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B23"/>
       <c r="C23"/>
       <c r="D23"/>
-      <c r="E23" s="12"/>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B24"/>
       <c r="C24"/>
       <c r="D24"/>
-      <c r="E24" s="12"/>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B25"/>
       <c r="C25"/>
       <c r="D25"/>
-      <c r="E25" s="12"/>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B26"/>
       <c r="C26"/>
       <c r="D26"/>
-      <c r="E26" s="12"/>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B27"/>
       <c r="C27"/>
       <c r="D27"/>
-      <c r="E27" s="12"/>
-    </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B28"/>
       <c r="C28"/>
       <c r="D28"/>
-      <c r="E28" s="12"/>
-    </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B29"/>
       <c r="C29"/>
       <c r="D29"/>
-      <c r="E29" s="12"/>
-    </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B30"/>
       <c r="C30"/>
       <c r="D30"/>
-      <c r="E30" s="12"/>
-    </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B31"/>
       <c r="C31"/>
       <c r="D31"/>
-      <c r="E31" s="12"/>
-    </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B32"/>
       <c r="C32"/>
       <c r="D32"/>
-      <c r="E32" s="12"/>
-    </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B33"/>
       <c r="C33"/>
       <c r="D33"/>
-      <c r="E33" s="12"/>
-    </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.2">
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B34"/>
       <c r="C34"/>
       <c r="D34"/>
-      <c r="E34" s="12"/>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
@@ -3271,16 +3044,16 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B2:I31"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.28515625" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.28515625" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="3.28515625" customWidth="1"/>
+    <col min="1" max="1" width="3.26953125" customWidth="1"/>
+    <col min="2" max="2" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.26953125" customWidth="1"/>
+    <col min="4" max="4" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:9" ht="13" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>27</v>
       </c>
@@ -3291,34 +3064,34 @@
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="2:9" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="19" t="s">
+    <row r="3" spans="2:9" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="E3" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="H3" s="19" t="s">
+      <c r="H3" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="I3" s="19" t="s">
+      <c r="I3" s="14" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B4" s="14" t="s">
+    <row r="4" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B4" s="10" t="s">
         <v>41</v>
       </c>
       <c r="D4" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" s="10" t="s">
         <v>36</v>
       </c>
       <c r="G4" t="s">
@@ -3327,16 +3100,15 @@
       <c r="H4" t="s">
         <v>36</v>
       </c>
-      <c r="I4" s="17">
+      <c r="I4" s="12">
         <v>3.6</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B5" s="5"/>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.25">
       <c r="D5" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="10" t="s">
         <v>38</v>
       </c>
       <c r="G5" t="s">
@@ -3345,12 +3117,11 @@
       <c r="H5" t="s">
         <v>48</v>
       </c>
-      <c r="I5" s="17">
+      <c r="I5" s="12">
         <v>1000</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B6" s="5"/>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.25">
       <c r="D6" t="s">
         <v>32</v>
       </c>
@@ -3363,54 +3134,51 @@
       <c r="H6" t="s">
         <v>50</v>
       </c>
-      <c r="I6" s="17">
+      <c r="I6" s="12">
         <v>1000</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B7" s="5"/>
-    </row>
-    <row r="18" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D18" s="17"/>
-    </row>
-    <row r="19" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D19" s="17"/>
-    </row>
-    <row r="20" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D20" s="17"/>
-    </row>
-    <row r="21" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D21" s="18"/>
-    </row>
-    <row r="22" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D22" s="17"/>
-    </row>
-    <row r="23" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D23" s="17"/>
-    </row>
-    <row r="24" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D24" s="17"/>
-    </row>
-    <row r="25" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D25" s="17"/>
-    </row>
-    <row r="26" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D26" s="17"/>
-    </row>
-    <row r="27" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D27" s="17"/>
-    </row>
-    <row r="28" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D28" s="17"/>
-    </row>
-    <row r="29" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D29" s="17"/>
-    </row>
-    <row r="30" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D30" s="17"/>
-    </row>
-    <row r="31" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D31" s="17"/>
+    <row r="18" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D18" s="12"/>
+    </row>
+    <row r="19" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D19" s="12"/>
+    </row>
+    <row r="20" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D20" s="12"/>
+    </row>
+    <row r="21" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D21" s="13"/>
+    </row>
+    <row r="22" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D22" s="12"/>
+    </row>
+    <row r="23" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D23" s="12"/>
+    </row>
+    <row r="24" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D24" s="12"/>
+    </row>
+    <row r="25" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D25" s="12"/>
+    </row>
+    <row r="26" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D26" s="12"/>
+    </row>
+    <row r="27" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D27" s="12"/>
+    </row>
+    <row r="28" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D28" s="12"/>
+    </row>
+    <row r="29" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D29" s="12"/>
+    </row>
+    <row r="30" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D30" s="12"/>
+    </row>
+    <row r="31" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D31" s="12"/>
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>

--- a/SysSettings.xlsx
+++ b/SysSettings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gaura\Documents\GitHub\DemoS_001\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DA3BB94-89E2-4D76-9132-41913A6AB15A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB55F90D-1DCD-49E3-A200-A91A4C845142}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="853" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="853" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Region-Time Slices" sheetId="16" r:id="rId1"/>
@@ -2729,7 +2729,7 @@
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="17">
-        <v>20025</v>
+        <v>2025</v>
       </c>
       <c r="C4" s="17"/>
       <c r="D4" s="17" t="s">

--- a/SysSettings.xlsx
+++ b/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gaura\Documents\GitHub\DemoS_001\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB55F90D-1DCD-49E3-A200-A91A4C845142}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C047F67-E1B9-4994-832F-10112A708DC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="853" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -903,7 +903,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>the start year of the model (2005);</a:t>
+            <a:t>the start year of the model (2025);</a:t>
           </a:r>
         </a:p>
         <a:p>
